--- a/outputs/daily/hr_rankings_2026-09-17_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-17_full.xlsx
@@ -1299,22 +1299,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>656941</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>74.90000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>30.2</v>
+        <v>60.5</v>
       </c>
       <c r="R4" t="n">
-        <v>65.3</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1381,7 +1381,7 @@
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>40.1</v>
+        <v>60.7</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1390,33 +1390,37 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1433,12 +1437,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1453,122 +1457,122 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.1156</t>
+          <t>103.0426</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5229</t>
+          <t>0.4769</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2812</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3758</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>77.16</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>41.56</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.2297</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3478</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -1579,22 +1583,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>656941</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1614,12 +1618,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1628,7 +1632,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1642,65 +1646,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>60.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.5</v>
+        <v>30.2</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>65.3</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>60.7</v>
+        <v>40.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1737,122 +1737,122 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>103.0426</t>
+          <t>104.1156</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4769</t>
+          <t>0.5229</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2812</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3758</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.16</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>75.42</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>54.49</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2297</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.3478</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3063,7 +3063,7 @@
         <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3073,14 +3073,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>3</t>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bobby Witt</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>58.6</v>
+        <v>59.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3347,7 +3347,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3357,14 +3357,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>2</t>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -7195,27 +7195,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>690993</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7225,17 +7225,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>607200</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7258,26 +7258,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>46.7</v>
+        <v>36.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>60.5</v>
+        <v>48.1</v>
       </c>
       <c r="R25" t="n">
-        <v>41.1</v>
+        <v>48.6</v>
       </c>
       <c r="S25" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>12</v>
+        <v>35.6</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -7333,142 +7333,142 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>11.44</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>100.7796</t>
+          <t>100.3346</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.4591</t>
+          <t>0.4328</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.2065</t>
+          <t>0.1625</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>37.38</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1673</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.08</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.4477</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7479,47 +7479,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>686469</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>52.6</v>
+        <v>52.2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7542,26 +7542,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>40.5</v>
+        <v>49.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>60.5</v>
+        <v>38.6</v>
       </c>
       <c r="R26" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S26" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T26" t="n">
         <v>80</v>
       </c>
       <c r="U26" t="n">
-        <v>25.3</v>
+        <v>56.2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -7622,137 +7622,129 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 18.0 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>100.2834</t>
+          <t>102.03</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4301</t>
+          <t>0.4294</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.2205</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.3936</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7763,27 +7755,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>690993</t>
+          <t>683146</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-17T23:40:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7793,17 +7785,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>607200</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7812,7 +7804,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7826,26 +7818,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>36.1</v>
+        <v>44.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="R27" t="n">
-        <v>48.6</v>
+        <v>65.3</v>
       </c>
       <c r="S27" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T27" t="n">
         <v>80</v>
       </c>
       <c r="U27" t="n">
-        <v>35.6</v>
+        <v>45.3</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7859,7 +7851,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7901,12 +7893,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7916,12 +7908,12 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 6/20, 1 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 29.2 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -7931,102 +7923,102 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>43.26</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>100.3346</t>
+          <t>101.7196</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4328</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1625</t>
+          <t>0.1749</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>75.08</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>54.07</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>35.33</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4477</t>
+          <t>0.4142</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1724</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -8036,7 +8028,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8047,47 +8039,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-18T00:05:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8096,7 +8088,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>52.2</v>
+        <v>51.8</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8110,40 +8102,40 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>49.6</v>
+        <v>27.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>38.6</v>
+        <v>60.5</v>
       </c>
       <c r="R28" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S28" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T28" t="n">
         <v>80</v>
       </c>
       <c r="U28" t="n">
-        <v>56.2</v>
+        <v>55.9</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -8158,17 +8150,17 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -8185,134 +8177,142 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 18.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>102.03</t>
+          <t>98.7239</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.4294</t>
+          <t>0.3936</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.1416</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.3346</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>49.01</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.2205</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.3936</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="inlineStr"/>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -8323,22 +8323,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>683146</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8386,40 +8386,40 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>44.2</v>
+        <v>46.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>47.7</v>
+        <v>60.5</v>
       </c>
       <c r="R29" t="n">
-        <v>65.3</v>
+        <v>41.1</v>
       </c>
       <c r="S29" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T29" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U29" t="n">
-        <v>45.3</v>
+        <v>12</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8434,17 +8434,17 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -8461,142 +8461,142 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 29.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.44</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.7196</t>
+          <t>100.7796</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.4591</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1749</t>
+          <t>0.2065</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>75.08</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>54.07</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.1673</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4142</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1724</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -11975,27 +11975,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>670231</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>John Rave</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-17T23:40:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -12005,17 +12005,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>607200</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -12038,65 +12038,57 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>41.8</v>
+        <v>32.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>48.1</v>
+        <v>60.5</v>
       </c>
       <c r="R42" t="n">
-        <v>48.6</v>
+        <v>41.1</v>
       </c>
       <c r="S42" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T42" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U42" t="n">
-        <v>22.6</v>
+        <v>45.1</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
@@ -12113,142 +12105,142 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>88.16</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>100.4725</t>
+          <t>99.9569</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.4629</t>
+          <t>0.3805</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.1955</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3132</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.1904</t>
+          <t>0.1929</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.4477</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12259,47 +12251,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-17T19:10:00Z</t>
+          <t>2026-09-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>607200</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12308,7 +12300,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12322,61 +12314,65 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>27.2</v>
+        <v>41.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>39.8</v>
+        <v>48.1</v>
       </c>
       <c r="R43" t="n">
-        <v>44.7</v>
+        <v>48.6</v>
       </c>
       <c r="S43" t="n">
-        <v>96.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U43" t="n">
-        <v>81.40000000000001</v>
+        <v>22.6</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -12393,7 +12389,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
@@ -12403,17 +12399,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/27, 1 HR</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 17.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -12423,112 +12419,112 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>98.7904</t>
+          <t>100.4725</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.4629</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1955</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
+          <t>28.71</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>0.1904</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>8.11</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>40.78</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>89.08</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>0.4477</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>0.186</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
           <t>29.4</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.202</t>
-        </is>
-      </c>
-      <c r="BA43" t="inlineStr">
-        <is>
-          <t>9.37</t>
-        </is>
-      </c>
-      <c r="BB43" t="inlineStr">
-        <is>
-          <t>34.46</t>
-        </is>
-      </c>
-      <c r="BC43" t="inlineStr">
-        <is>
-          <t>87.24</t>
-        </is>
-      </c>
-      <c r="BD43" t="inlineStr">
-        <is>
-          <t>0.4123</t>
-        </is>
-      </c>
-      <c r="BE43" t="inlineStr">
-        <is>
-          <t>0.1744</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>27.75</t>
-        </is>
-      </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12539,47 +12535,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>682626</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T19:10:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12588,7 +12584,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12602,65 +12598,61 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>54.2</v>
+        <v>27.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>47.7</v>
+        <v>39.8</v>
       </c>
       <c r="R44" t="n">
-        <v>65.3</v>
+        <v>44.7</v>
       </c>
       <c r="S44" t="n">
-        <v>40.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U44" t="n">
-        <v>4.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -12677,7 +12669,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
@@ -12687,17 +12679,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 29.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -12707,112 +12699,112 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>102.9047</t>
+          <t>98.7904</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.4293</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.2003</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3232</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.1721</t>
+          <t>0.202</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>87.24</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.4142</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.1724</t>
+          <t>0.1744</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12823,27 +12815,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>701678</t>
+          <t>682626</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hao-Yu Lee</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-17T23:40:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12853,17 +12845,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>607200</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12872,7 +12864,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12886,26 +12878,26 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>33.9</v>
+        <v>54.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="R45" t="n">
-        <v>48.6</v>
+        <v>65.3</v>
       </c>
       <c r="S45" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T45" t="n">
         <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>29.2</v>
+        <v>4.2</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12919,7 +12911,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12944,7 +12936,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -12961,27 +12953,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 29.2 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -12991,102 +12983,102 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>100.1556</t>
+          <t>102.9047</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>0.4293</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.2003</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.3232</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1721</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.4477</t>
+          <t>0.4142</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1724</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
@@ -13096,7 +13088,7 @@
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -13107,27 +13099,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>701678</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Hao-Yu Lee</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -13137,17 +13129,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>607200</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -13156,7 +13148,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -13170,61 +13162,65 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>31.5</v>
+        <v>33.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>52.8</v>
+        <v>48.1</v>
       </c>
       <c r="R46" t="n">
-        <v>41.1</v>
+        <v>48.6</v>
       </c>
       <c r="S46" t="n">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T46" t="n">
         <v>50</v>
       </c>
       <c r="U46" t="n">
-        <v>61.7</v>
+        <v>29.2</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -13241,12 +13237,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -13256,12 +13252,12 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -13271,112 +13267,112 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>89.34</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>99.9889</t>
+          <t>100.1556</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4174</t>
+          <t>0.389</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.1515</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3106</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.08</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.4477</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13387,47 +13383,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-17T19:10:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -13436,7 +13432,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -13454,22 +13450,22 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>28.3</v>
+        <v>31.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>61.7</v>
+        <v>52.8</v>
       </c>
       <c r="R47" t="n">
-        <v>44.7</v>
+        <v>41.1</v>
       </c>
       <c r="S47" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T47" t="n">
         <v>50</v>
       </c>
       <c r="U47" t="n">
-        <v>54.3</v>
+        <v>61.7</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -13483,7 +13479,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -13526,7 +13522,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13536,127 +13532,127 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 9/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 17.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>100.1995</t>
+          <t>99.9889</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>0.3815</t>
+          <t>0.4174</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>0.1306</t>
+          <t>0.1515</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.3106</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>18.26</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>0.1077</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>0.4838</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>0.2111</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr"/>
@@ -13667,24 +13663,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>681393</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>2026-09-17T19:10:00Z</t>
@@ -13697,17 +13693,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -13716,7 +13712,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13730,26 +13726,26 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>31</v>
+        <v>28.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>41.7</v>
+        <v>61.7</v>
       </c>
       <c r="R48" t="n">
         <v>44.7</v>
       </c>
       <c r="S48" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T48" t="n">
         <v>50</v>
       </c>
       <c r="U48" t="n">
-        <v>62.8</v>
+        <v>54.3</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13763,7 +13759,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -13801,12 +13797,12 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -13816,112 +13812,112 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 17.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>98.232</t>
+          <t>100.1995</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>0.3792</t>
+          <t>0.3815</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1306</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>43.24</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1077</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>87.24</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.4838</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>0.1744</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
@@ -13947,47 +13943,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>681393</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T19:10:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13996,7 +13992,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -14010,26 +14006,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>35.6</v>
+        <v>31</v>
       </c>
       <c r="Q49" t="n">
-        <v>52.8</v>
+        <v>41.7</v>
       </c>
       <c r="R49" t="n">
-        <v>41.1</v>
+        <v>44.7</v>
       </c>
       <c r="S49" t="n">
-        <v>76.2</v>
+        <v>100</v>
       </c>
       <c r="T49" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -14043,7 +14039,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14081,142 +14077,142 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>99.4425</t>
+          <t>98.232</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.3974</t>
+          <t>0.3792</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1676</t>
+          <t>0.1564</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.2976</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>73.71</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.24</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1744</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14227,47 +14223,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-18T01:38:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14290,65 +14286,61 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>52.6</v>
+        <v>35.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>20.4</v>
+        <v>52.8</v>
       </c>
       <c r="R50" t="n">
-        <v>28.2</v>
+        <v>41.1</v>
       </c>
       <c r="S50" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T50" t="n">
         <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>37.8</v>
+        <v>0</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -14365,27 +14357,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14395,104 +14387,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>91.99</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>101.4875</t>
+          <t>99.4425</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4594</t>
+          <t>0.3974</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.2097</t>
+          <t>0.1676</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3345</t>
+          <t>0.2976</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>73.71</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.2266</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="inlineStr"/>
+          <t>28.76</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14503,47 +14503,47 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665019</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-18T01:38:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14552,7 +14552,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14566,61 +14566,65 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>38.6</v>
+        <v>52.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.8</v>
+        <v>20.4</v>
       </c>
       <c r="R51" t="n">
-        <v>41.1</v>
+        <v>28.2</v>
       </c>
       <c r="S51" t="n">
-        <v>64.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>80</v>
       </c>
       <c r="U51" t="n">
-        <v>10.6</v>
+        <v>37.8</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -14637,27 +14641,27 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -14667,112 +14671,104 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>91.99</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>101.0072</t>
+          <t>101.4875</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.4594</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.1613</t>
+          <t>0.2097</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.2836</t>
+          <t>0.3345</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.1451</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>28.76</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH51" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -14783,12 +14779,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>686681</t>
+          <t>672580</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Maikel Garcia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -14813,7 +14809,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -14832,7 +14828,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14846,11 +14842,11 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="Q52" t="n">
         <v>60.5</v>
@@ -14859,27 +14855,27 @@
         <v>41.1</v>
       </c>
       <c r="S52" t="n">
-        <v>59.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>55.9</v>
+        <v>20.9</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -14894,12 +14890,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -14921,7 +14917,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
@@ -14931,17 +14927,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Contact streak: 10/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -14951,67 +14947,67 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>98.7239</t>
+          <t>100.5105</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.3936</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.1416</t>
+          <t>0.1138</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.2958</t>
+          <t>0.3224</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>71.83</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>49.01</t>
+          <t>34.81</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -15067,56 +15063,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>575929</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Willson Contreras</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-18T00:05:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tyler Alexander</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>641302</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15130,62 +15126,58 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>56.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>17.7</v>
+        <v>52.8</v>
       </c>
       <c r="R53" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S53" t="n">
-        <v>90.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T53" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U53" t="n">
-        <v>26.4</v>
+        <v>10.6</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15210,22 +15202,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 1 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.5% barrel, 4.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15235,104 +15227,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>102.6842</t>
+          <t>101.0072</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.4873</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>0.1613</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3713</t>
+          <t>0.2836</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1451</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.1097</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>24.23</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr"/>
-      <c r="BH53" t="inlineStr"/>
+          <t>28.76</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15343,47 +15343,47 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>575929</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-17T17:10:00Z</t>
+          <t>2026-09-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Tyler Alexander</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>605488</t>
+          <t>641302</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>46.9</v>
+        <v>48</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15406,60 +15406,60 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>45.5</v>
+        <v>56.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>46.5</v>
+        <v>17.7</v>
       </c>
       <c r="R54" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S54" t="n">
-        <v>52.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T54" t="n">
         <v>78</v>
       </c>
       <c r="U54" t="n">
-        <v>5.1</v>
+        <v>26.4</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>order MLB 8 vs RotoWire 7</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -15481,142 +15481,134 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 0 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 31.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 4.8 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>45.71</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>91.84</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>102.7272</t>
+          <t>102.6842</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t>0.4873</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1646</t>
+          <t>0.231</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.3202</t>
+          <t>0.3713</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>46.31</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.4429</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1918</t>
+          <t>0.1097</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>32.02</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH54" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>24.23</t>
+        </is>
+      </c>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15627,27 +15619,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>687957</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-17T19:10:00Z</t>
+          <t>2026-09-17T17:10:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15657,26 +15649,26 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>605488</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15690,26 +15682,26 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>5.4</v>
+        <v>45.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>61.7</v>
+        <v>46.5</v>
       </c>
       <c r="R55" t="n">
-        <v>44.7</v>
+        <v>41.1</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T55" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U55" t="n">
-        <v>45</v>
+        <v>5.1</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15723,7 +15715,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -15733,7 +15725,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -15741,7 +15733,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>order MLB 8 vs RotoWire 7</t>
+        </is>
+      </c>
       <c r="AC55" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15761,12 +15757,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -15776,12 +15772,12 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Contact streak: 10/23 over last 7 games</t>
+          <t>Last 7 games: 2/13, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 17.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 31.5 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15791,112 +15787,112 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>91.84</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>95.2817</t>
+          <t>102.7272</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.4082</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.1646</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3045</t>
+          <t>0.3202</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>67.03</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1136</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.4838</t>
+          <t>0.4429</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.2111</t>
+          <t>0.1918</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15907,47 +15903,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T19:10:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15970,26 +15966,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>40.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>52.8</v>
+        <v>61.7</v>
       </c>
       <c r="R56" t="n">
-        <v>41.1</v>
+        <v>44.7</v>
       </c>
       <c r="S56" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U56" t="n">
-        <v>49.9</v>
+        <v>45</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -16003,7 +15999,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -16041,142 +16037,142 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>101.3692</t>
+          <t>95.2817</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4117</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1739</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3145</t>
+          <t>0.3045</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>67.03</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1654</t>
+          <t>0.1136</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.4838</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16187,24 +16183,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>672580</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Maikel Garcia</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>2026-09-17T23:15:00Z</t>
@@ -16217,17 +16213,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16236,7 +16232,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -16250,65 +16246,61 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>26.6</v>
+        <v>40.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>60.5</v>
+        <v>52.8</v>
       </c>
       <c r="R57" t="n">
         <v>41.1</v>
       </c>
       <c r="S57" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T57" t="n">
         <v>50</v>
       </c>
       <c r="U57" t="n">
-        <v>20.9</v>
+        <v>49.9</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16325,127 +16317,127 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>100.5105</t>
+          <t>101.3692</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.4117</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1138</t>
+          <t>0.1739</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3224</t>
+          <t>0.3145</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>71.83</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1294</t>
+          <t>0.1654</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
@@ -21853,7 +21845,7 @@
         <v>50</v>
       </c>
       <c r="U77" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21910,7 +21902,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -21920,7 +21912,7 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Last 7 games: 5/28, 1 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
@@ -24843,22 +24835,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -24873,17 +24865,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24906,26 +24898,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>6.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q88" t="n">
-        <v>30.2</v>
+        <v>60.3</v>
       </c>
       <c r="R88" t="n">
-        <v>65.3</v>
+        <v>41.1</v>
       </c>
       <c r="S88" t="n">
-        <v>94.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T88" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U88" t="n">
-        <v>28.2</v>
+        <v>8.5</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24934,33 +24926,37 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24977,12 +24973,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -24992,127 +24988,127 @@
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>86.24</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>93.8724</t>
+          <t>99.826</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.3714</t>
+          <t>0.3247</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.0851</t>
+          <t>0.0948</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.3051</t>
+          <t>0.3052</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>62.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>28.31</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1098</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.3478</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -25123,27 +25119,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>668670</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jake Rogers</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-17T23:40:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -25153,22 +25149,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -25186,26 +25182,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>29.1</v>
+        <v>6.9</v>
       </c>
       <c r="Q89" t="n">
-        <v>34.5</v>
+        <v>30.2</v>
       </c>
       <c r="R89" t="n">
-        <v>48.6</v>
+        <v>65.3</v>
       </c>
       <c r="S89" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T89" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -25219,7 +25215,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -25257,12 +25253,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -25272,12 +25268,12 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -25287,102 +25283,102 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>86.24</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>98.1269</t>
+          <t>93.8724</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.3077</t>
+          <t>0.3714</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.0851</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.2705</t>
+          <t>0.3051</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>28.31</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.1098</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.3478</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH89" t="inlineStr">
@@ -25392,7 +25388,7 @@
       </c>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25403,56 +25399,56 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>694203</t>
+          <t>668670</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Jake Rogers</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-18T01:38:00Z</t>
+          <t>2026-09-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>40.9</v>
+        <v>41.2</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -25466,62 +25462,58 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>24.5</v>
+        <v>29.1</v>
       </c>
       <c r="Q90" t="n">
-        <v>48.1</v>
+        <v>34.5</v>
       </c>
       <c r="R90" t="n">
-        <v>28.2</v>
+        <v>48.6</v>
       </c>
       <c r="S90" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T90" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U90" t="n">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25541,27 +25533,27 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -25571,104 +25563,112 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>98.6955</t>
+          <t>98.1269</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.3077</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.1127</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.2705</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1348</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.3885</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>29.12</t>
-        </is>
-      </c>
-      <c r="BG90" t="inlineStr"/>
-      <c r="BH90" t="inlineStr"/>
+          <t>18.04</t>
+        </is>
+      </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25679,47 +25679,47 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-18T01:38:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>40.6</v>
+        <v>40.9</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25742,26 +25742,26 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>21.7</v>
+        <v>24.5</v>
       </c>
       <c r="Q91" t="n">
-        <v>60.3</v>
+        <v>48.1</v>
       </c>
       <c r="R91" t="n">
-        <v>41.1</v>
+        <v>28.2</v>
       </c>
       <c r="S91" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T91" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>8.5</v>
+        <v>50.3</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr"/>
@@ -25817,142 +25817,134 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>99.826</t>
+          <t>98.6955</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.3247</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.0948</t>
+          <t>0.1127</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3052</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.3885</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="BG91" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH91" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>29.12</t>
+        </is>
+      </c>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -27075,47 +27067,47 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-18T01:38:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -27138,40 +27130,40 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>39.7</v>
+        <v>11.9</v>
       </c>
       <c r="Q96" t="n">
-        <v>20.4</v>
+        <v>60.5</v>
       </c>
       <c r="R96" t="n">
-        <v>28.2</v>
+        <v>41.1</v>
       </c>
       <c r="S96" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T96" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -27186,12 +27178,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -27218,7 +27210,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -27228,119 +27220,127 @@
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.6% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>41.12</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>100.8686</t>
+          <t>98.8128</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.4287</t>
+          <t>0.3026</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.1822</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.3419</t>
+          <t>0.2573</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.1912</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="BG96" t="inlineStr"/>
-      <c r="BH96" t="inlineStr"/>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="BG96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH96" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -27351,56 +27351,56 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>641584</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jake Fraley</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-17T17:10:00Z</t>
+          <t>2026-09-18T01:38:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>605488</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -27414,39 +27414,47 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>17.7</v>
+        <v>39.7</v>
       </c>
       <c r="Q97" t="n">
-        <v>46.5</v>
+        <v>20.4</v>
       </c>
       <c r="R97" t="n">
-        <v>41.1</v>
+        <v>28.2</v>
       </c>
       <c r="S97" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T97" t="n">
         <v>50</v>
       </c>
       <c r="U97" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z97" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -27454,17 +27462,17 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -27481,12 +27489,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -27496,127 +27504,119 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 31.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.6% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>41.12</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>95.9479</t>
+          <t>100.8686</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.3564</t>
+          <t>0.4287</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.1378</t>
+          <t>0.1822</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.2905</t>
+          <t>0.3419</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>46.92</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>26.24</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.1529</t>
+          <t>0.1912</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.4429</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.1918</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>32.02</t>
-        </is>
-      </c>
-      <c r="BG97" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH97" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="BG97" t="inlineStr"/>
+      <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27627,56 +27627,56 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>641584</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Jake Fraley</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T17:10:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>605488</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -27690,65 +27690,57 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>11.9</v>
+        <v>17.7</v>
       </c>
       <c r="Q98" t="n">
-        <v>60.5</v>
+        <v>46.5</v>
       </c>
       <c r="R98" t="n">
         <v>41.1</v>
       </c>
       <c r="S98" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T98" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U98" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr"/>
@@ -27765,7 +27757,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
@@ -27780,12 +27772,12 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 31.5 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
@@ -27795,97 +27787,97 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>84.29</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>98.8128</t>
+          <t>95.9479</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.3026</t>
+          <t>0.3564</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.0777</t>
+          <t>0.1378</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.2573</t>
+          <t>0.2905</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>46.92</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>26.24</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.1529</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.4429</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1918</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr">
@@ -27900,7 +27892,7 @@
       </c>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -36881,22 +36873,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>656941</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -36916,12 +36908,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -36948,13 +36940,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>74.90000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>30.2</v>
+        <v>60.5</v>
       </c>
       <c r="R4" t="n">
-        <v>65.3</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -36963,7 +36955,7 @@
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>40.1</v>
+        <v>60.7</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -36972,33 +36964,37 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -37015,12 +37011,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -37035,122 +37031,122 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.1156</t>
+          <t>103.0426</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5229</t>
+          <t>0.4769</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2812</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3758</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>77.16</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>41.56</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.2297</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3478</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -37161,22 +37157,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>656941</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -37196,12 +37192,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -37210,7 +37206,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -37224,65 +37220,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>60.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.5</v>
+        <v>30.2</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>65.3</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>60.7</v>
+        <v>40.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -37299,12 +37291,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -37319,122 +37311,122 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>103.0426</t>
+          <t>104.1156</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4769</t>
+          <t>0.5229</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2812</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3758</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.16</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>75.42</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>54.49</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2297</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.3478</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -38618,7 +38610,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -38632,7 +38624,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -38645,7 +38637,7 @@
         <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -38655,14 +38647,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>3</t>
@@ -38680,12 +38672,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -38858,7 +38850,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bobby Witt</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -38902,7 +38894,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>58.6</v>
+        <v>59.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -38916,7 +38908,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -38929,7 +38921,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -38939,14 +38931,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>2</t>
@@ -38964,12 +38956,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
